--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104698_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104698_W27.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2354</v>
+        <v>6.7545</v>
       </c>
       <c r="E2" t="n">
-        <v>4.427</v>
+        <v>4.0276</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8084</v>
+        <v>2.7269</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2154</v>
+        <v>3.0686</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7835</v>
+        <v>0.1668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4319</v>
+        <v>2.9018</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4275</v>
+        <v>2.4209</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6438</v>
+        <v>0.0377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7837</v>
+        <v>2.3832</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2121</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1397</v>
+        <v>0.129</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3517</v>
+        <v>0.5187</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1011</v>
+        <v>1.7769</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1221</v>
+        <v>1.2912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.979</v>
+        <v>0.4857</v>
       </c>
       <c r="V2" t="n">
-        <v>4.1458</v>
+        <v>0.3155</v>
       </c>
       <c r="W2" t="n">
-        <v>4.1458</v>
+        <v>0.3155</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1742</v>
+        <v>6.249</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2759</v>
+        <v>3.937</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8984</v>
+        <v>2.312</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0704</v>
+        <v>1.227</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1703</v>
+        <v>0.784</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9001</v>
+        <v>0.4429</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4331</v>
+        <v>1.409</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0448</v>
+        <v>0.627</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3883</v>
+        <v>0.782</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6373</v>
+        <v>-0.1821</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1255</v>
+        <v>0.157</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5118</v>
+        <v>-0.3391</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1945</v>
+        <v>1.121</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5213</v>
+        <v>0.6756</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6732</v>
+        <v>0.4454</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3214</v>
+        <v>4.1287</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>4.1287</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8376</v>
+        <v>3.8671</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7444</v>
+        <v>1.6105</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0932</v>
+        <v>2.2566</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6811</v>
+        <v>3.686</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4847</v>
+        <v>1.4903</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1964</v>
+        <v>2.1957</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7945</v>
+        <v>3.7666</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1878</v>
+        <v>1.1754</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6068</v>
+        <v>2.5912</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1134</v>
+        <v>-0.0806</v>
       </c>
       <c r="N4" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0042</v>
+        <v>0.0234</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0575</v>
+        <v>-0.0375</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0617</v>
+        <v>0.0609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1703</v>
+        <v>3.3729</v>
       </c>
       <c r="E5" t="n">
-        <v>2.415</v>
+        <v>2.4623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7553</v>
+        <v>0.9106</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2009</v>
+        <v>1.2153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9263</v>
+        <v>0.9303</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2746</v>
+        <v>0.285</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6322</v>
+        <v>1.6266</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4312</v>
+        <v>-0.4113</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2358</v>
+        <v>1.4355</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5444</v>
+        <v>0.6176</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6914</v>
+        <v>0.8179</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.336</v>
+        <v>1.4953</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1608</v>
+        <v>0.281</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8248</v>
+        <v>1.2143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5091</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4211</v>
+        <v>0.5097</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0621</v>
+        <v>0.2556</v>
       </c>
       <c r="K6" t="n">
-        <v>0.876</v>
+        <v>0.1067</v>
       </c>
       <c r="L6" t="n">
-        <v>1.186</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.553</v>
+        <v>0.2741</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.788</v>
+        <v>-0.0866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2826</v>
+        <v>0.1429</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2744</v>
+        <v>0.0253</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1176</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4141</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2739</v>
+        <v>0.7893</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1358</v>
+        <v>-1.7555</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4097</v>
+        <v>2.5448</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5226</v>
+        <v>0.413</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0187</v>
+        <v>-0.4165</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5038</v>
+        <v>0.8295</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2634</v>
+        <v>-0.652</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1141</v>
+        <v>-1.4931</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>0.8411</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2592</v>
+        <v>1.065</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0954</v>
+        <v>1.0766</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0614</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3992</v>
+        <v>0.0346</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3378</v>
+        <v>0.7482</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5886</v>
+        <v>0.7046</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3818</v>
+        <v>-1.1065</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9704</v>
+        <v>1.8111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5928</v>
+        <v>-0.5986</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1601</v>
+        <v>-2.1625</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5673</v>
+        <v>1.5639</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7506</v>
+        <v>-0.7741</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2379</v>
+        <v>-2.2483</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1578</v>
+        <v>0.1755</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>1.635</v>
+        <v>1.7584</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5444</v>
+        <v>0.8545</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0906</v>
+        <v>0.9039</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3052</v>
+        <v>0.3888</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3239</v>
+        <v>2.0869</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0187</v>
+        <v>-1.698</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4172</v>
+        <v>0.5012</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.417</v>
+        <v>0.089</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8343</v>
+        <v>0.4122</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6333</v>
+        <v>2.0337</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4861</v>
+        <v>0.8651</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8529</v>
+        <v>1.1686</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0505</v>
+        <v>-1.5325</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0691</v>
+        <v>-0.7761</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0186</v>
+        <v>-0.7563</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3103</v>
+        <v>1.3413</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>1.24</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2462</v>
+        <v>0.1013</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9436</v>
+        <v>-1.0409</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8579</v>
+        <v>-2.2423</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9143</v>
+        <v>1.2013</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9863</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2106</v>
+        <v>-0.2124</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7756</v>
+        <v>-0.773</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9633</v>
+        <v>-0.9902</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N10" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.0068</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6775</v>
+        <v>-0.0166</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2383</v>
+        <v>0.0097</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3504</v>
+        <v>-4.856</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.2158</v>
+        <v>-8.7875</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8654</v>
+        <v>3.9315</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4538</v>
+        <v>-1.4571</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3361</v>
+        <v>-2.3405</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8823</v>
+        <v>0.8834</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7284</v>
+        <v>-2.7526</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0588</v>
+        <v>-3.0724</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2746</v>
+        <v>1.2955</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7346</v>
+        <v>1.2416</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3176</v>
+        <v>0.794</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4171</v>
+        <v>0.4476</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.0168</v>
+        <v>17.7246</v>
       </c>
       <c r="E12" t="n">
-        <v>0.107899999999999</v>
+        <v>0.5134999999999987</v>
       </c>
       <c r="F12" t="n">
-        <v>16.909</v>
+        <v>17.2111</v>
       </c>
       <c r="G12" t="n">
-        <v>7.583799999999999</v>
+        <v>7.599699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6523</v>
+        <v>-1.6515</v>
       </c>
       <c r="I12" t="n">
-        <v>9.2362</v>
+        <v>9.251100000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>6.537199999999999</v>
+        <v>6.343500000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.7645</v>
+        <v>-3.8715</v>
       </c>
       <c r="L12" t="n">
-        <v>10.3018</v>
+        <v>10.2149</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0467</v>
+        <v>1.2561</v>
       </c>
       <c r="N12" t="n">
-        <v>2.1123</v>
+        <v>2.2199</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0653</v>
+        <v>-0.9636999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.5367</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-22.6832</v>
+        <v>-22.7631</v>
       </c>
       <c r="R12" t="n">
-        <v>18.1467</v>
+        <v>18.2106</v>
       </c>
       <c r="S12" t="n">
-        <v>8.8919</v>
+        <v>9.617000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7485</v>
+        <v>5.4787</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1435</v>
+        <v>4.138199999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>5.0778</v>
+        <v>5.0605</v>
       </c>
       <c r="W12" t="n">
-        <v>11.5054</v>
+        <v>11.4544</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.4277</v>
+        <v>-6.394</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4177</v>
+        <v>0.8388</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2344</v>
+        <v>1.2618</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6521</v>
+        <v>-0.423</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4513</v>
+        <v>1.9618</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7375</v>
+        <v>-1.7144</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1888</v>
+        <v>3.6762</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1103</v>
+        <v>1.585</v>
       </c>
       <c r="K13" t="n">
-        <v>0.377</v>
+        <v>-2.3172</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2666</v>
+        <v>3.9022</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5617</v>
+        <v>0.3768</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3605</v>
+        <v>0.6028</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9222</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0129</v>
+        <v>-0.6772</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1179</v>
+        <v>-0.3232</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1308</v>
+        <v>-0.354</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1853</v>
+        <v>-2.4945</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1005</v>
+        <v>-0.1846</v>
       </c>
       <c r="E14" t="n">
-        <v>0.931</v>
+        <v>-0.3708</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8305</v>
+        <v>0.1862</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9712</v>
+        <v>-0.1985</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7098</v>
+        <v>-0.3564</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6811</v>
+        <v>0.1579</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6084</v>
+        <v>0.0172</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.3071</v>
+        <v>0.0172</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9156</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3628</v>
+        <v>-0.2157</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.3736</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2345</v>
+        <v>0.1579</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.2137</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.1604</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.0534</v>
+      </c>
+      <c r="V14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.0415</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.4055</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.6775</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.728</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-2.5068</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3705</v>
+        <v>-0.2448</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4878</v>
+        <v>0.3875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1173</v>
+        <v>-0.6323</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2035</v>
+        <v>-0.3311</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3608</v>
+        <v>1.6142</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1573</v>
+        <v>-1.9453</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0173</v>
+        <v>0.9568</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0173</v>
+        <v>1.672</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2209</v>
+        <v>-1.2879</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3781</v>
+        <v>-0.0578</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>-1.2301</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3938</v>
+        <v>-0.1511</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2782</v>
+        <v>-0.1141</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1155</v>
+        <v>-0.037</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.2179</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7899</v>
+        <v>-0.3714</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.778</v>
+        <v>-0.621</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0119</v>
+        <v>0.2495</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5599</v>
+        <v>-0.4631</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1414</v>
+        <v>0.7272</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4185</v>
+        <v>-1.1903</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6344</v>
+        <v>0.0785</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.3545</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6344</v>
+        <v>-0.276</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0745</v>
+        <v>-0.5416</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1414</v>
+        <v>0.3727</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2159</v>
+        <v>-0.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2156</v>
+        <v>0.2219</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2782</v>
+        <v>-0.4718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0626</v>
+        <v>0.6937</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8374</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2001</v>
+        <v>-0.7839</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3626</v>
+        <v>0.0859</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2982</v>
+        <v>0.5621</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7489</v>
+        <v>0.1435</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0471</v>
+        <v>0.4186</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1415</v>
+        <v>0.633</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3565</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4981</v>
+        <v>0.633</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1567</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3923</v>
+        <v>0.1435</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.549</v>
+        <v>-0.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8147</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>2.722</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0935</v>
+        <v>-0.122</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7561</v>
+        <v>-0.2788</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6627</v>
+        <v>0.1568</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.042</v>
+        <v>-0.8739</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0456</v>
+        <v>1.4021</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0876</v>
+        <v>-2.276</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3323</v>
+        <v>-0.7441</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6161</v>
+        <v>0.396</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9485</v>
+        <v>-1.1401</v>
       </c>
       <c r="J18" t="n">
-        <v>0.968</v>
+        <v>0.6869</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6797</v>
+        <v>0.3825</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7117</v>
+        <v>0.3045</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3003</v>
+        <v>-1.431</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0636</v>
+        <v>0.0135</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2368</v>
+        <v>-1.4446</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9448</v>
+        <v>-1.1882</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4688</v>
+        <v>-0.7809</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4761</v>
+        <v>-0.4074</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2185</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2185</v>
+        <v>-2.9416</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0901</v>
+        <v>-0.9911</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5461</v>
+        <v>-2.5718</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.544</v>
+        <v>1.5808</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8969</v>
+        <v>-1.2971</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3794</v>
+        <v>0.7496</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4825</v>
+        <v>-2.0467</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1352</v>
+        <v>-1.1568</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4413</v>
+        <v>0.348</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3061</v>
+        <v>-1.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7617</v>
+        <v>-0.1403</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0619</v>
+        <v>0.4016</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8236</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6306</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1179</v>
+        <v>0.406</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5127</v>
+        <v>-0.4771</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1505</v>
+        <v>-0.5334</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3112</v>
+        <v>-0.5334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.784</v>
+        <v>-1.1989</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9689</v>
+        <v>-0.6845</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7529</v>
+        <v>-0.5144</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7381</v>
+        <v>-0.8937</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3895</v>
+        <v>-1.3841</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1276</v>
+        <v>0.4904</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.1521</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3912</v>
+        <v>-1.4554</v>
       </c>
       <c r="L20" t="n">
-        <v>0.325</v>
+        <v>1.3033</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4543</v>
+        <v>-0.7416</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0017</v>
+        <v>0.0713</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4526</v>
+        <v>-0.8129</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0956</v>
+        <v>-0.7491</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2521</v>
+        <v>-0.2349</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8435</v>
+        <v>-0.5141</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7649</v>
+        <v>-1.1496</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.9502</v>
+        <v>-1.3074</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9445</v>
+        <v>-1.4567</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4243</v>
+        <v>-1.2435</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5202</v>
+        <v>-0.2131</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1246</v>
+        <v>0.1065</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6972</v>
+        <v>0.6612</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2752</v>
+        <v>-1.297</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9724</v>
+        <v>1.9582</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5726</v>
+        <v>-0.5548</v>
       </c>
       <c r="N21" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5739</v>
+        <v>-1.0592</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6696</v>
+        <v>-0.3899</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8292</v>
+        <v>-2.2163</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6148</v>
+        <v>-3.5437</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7856</v>
+        <v>1.3274</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.774</v>
+        <v>-0.7632</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5423</v>
+        <v>1.5532</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3163</v>
+        <v>-2.3164</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1937</v>
+        <v>-0.21</v>
       </c>
       <c r="K22" t="n">
-        <v>0.71</v>
+        <v>0.7067</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.9167</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5803</v>
+        <v>-0.5532</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8324</v>
+        <v>0.8465</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1083</v>
+        <v>-1.4924</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3912</v>
+        <v>-1.2756</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7171</v>
+        <v>-0.2168</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0654</v>
+        <v>-3.5664</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4487</v>
+        <v>-5.0681</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3833</v>
+        <v>1.5016</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4171</v>
+        <v>-4.4288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6768</v>
+        <v>0.675</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.0939</v>
+        <v>-5.1039</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.7777</v>
+        <v>-3.8015</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.8572</v>
+        <v>-3.8737</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6395</v>
+        <v>-0.6273</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3454</v>
+        <v>-0.1489</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7561</v>
+        <v>0.1691</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4107</v>
+        <v>-0.3181</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5527</v>
+        <v>0.5561</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>0.392</v>
+        <v>0.3983</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.782</v>
+        <v>-3.6952</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0277</v>
+        <v>-4.2857</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2457</v>
+        <v>0.5905</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1281</v>
+        <v>-1.1105</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3551</v>
+        <v>-0.3452</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7729</v>
+        <v>-0.7653</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5505</v>
+        <v>-0.5545</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5776</v>
+        <v>-0.556</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9754</v>
+        <v>-0.9002</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1693</v>
+        <v>-0.4046</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.806</v>
+        <v>-0.4956</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.0168</v>
+        <v>-14.6586</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.8164</v>
+        <v>-16.1216</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.200499999999999</v>
+        <v>1.4631</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.5838</v>
+        <v>-7.599699999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6522</v>
+        <v>1.6514</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.236000000000001</v>
+        <v>-9.251300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0468</v>
+        <v>-1.2563</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.112200000000001</v>
+        <v>-2.22</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0655</v>
+        <v>0.9637000000000004</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.537300000000001</v>
+        <v>-6.3436</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7643</v>
+        <v>3.8714</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.3015</v>
+        <v>-10.215</v>
       </c>
       <c r="P25" t="n">
-        <v>4.536700000000001</v>
+        <v>4.552700000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R25" t="n">
-        <v>22.6834</v>
+        <v>22.7632</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.891700000000002</v>
+        <v>-6.5511</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.1432</v>
+        <v>-4.1384</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.7485</v>
+        <v>-2.4129</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.0777</v>
+        <v>-5.0602</v>
       </c>
       <c r="W25" t="n">
-        <v>7.5202</v>
+        <v>7.4834</v>
       </c>
       <c r="X25" t="n">
-        <v>-12.5981</v>
+        <v>-12.5439</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104698_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104698_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.394</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2179</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.9416</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5334</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.3074</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.3983</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104698_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-12.5439</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
